--- a/config.xlsx
+++ b/config.xlsx
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -715,14 +715,9 @@
           <t>required_standalone_files</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TA.xml</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Exact filenames that must exist in every scenario folder.</t>
+          <t>Exact filenames that must exist in every scenario folder (rarely used).</t>
         </is>
       </c>
     </row>
@@ -746,227 +741,380 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>junction_scenario_prefixes</t>
+          <t>allowed_programs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CP, CB, CCCscp, CMCscp</t>
+          <t>AEB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Scenario families that require junction geometry checks (RD_03-06, SC_10).</t>
+          <t>Programs allowed as the 1st filename token, e.g. AEB (CH_NM_02).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>extra_scenario_prefixes</t>
+          <t>target_type_tokens</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CPLA, CPRA, CBNAO, CBFA, CMRs, CMRb, CMFtap, CMCscp</t>
+          <t>GVT, EPTa, EPTc, EBTa, EMT, SOV</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Extra valid scenario name prefixes that have no row in the Scenarios sheet.</t>
+          <t>Target-type tokens valid in the 4th filename slot: GVT, EPTa, EPTc, EBTa, EMT (CH_NM_02).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>junction_waypoint_radius_m</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>20</v>
+          <t>vut_speed_suffix</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VUT</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How close to a junction a waypoint must be to count as 'at the junction'.</t>
+          <t>Suffix marking the VUT-speed token in the filename (default VUT).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lane_width_tolerance_m</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.05</v>
+          <t>impact_suffix</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Imp</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Allowed deviation from the 3.5 m lane width.</t>
+          <t>Suffix marking the impact-overlap token in the filename (default Imp).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>junction_radius_tolerance_m</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.1</v>
+          <t>allowed_impact_overlaps</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0, 10, 25, 50, 75, 90, 100</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Allowed deviation from the 8 m junction radius.</t>
+          <t>Impact-overlap %s the filename token may take (CH_NM_02); exact value is checked by SC_16/17.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>impact_tolerance_pct</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>5</v>
+          <t>functional_file_pattern</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ENCAP_Scenario_func_{base}.xlsm</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Allowed deviation for crossing/turning impact % (CH_SC_16).</t>
+          <t>ENCAP functional/Test-Automation workbook name; {base} = scenario base name (CH_FB_01).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>longitudinal_impact_tolerance_pct</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
+          <t>macro_file_pattern</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MACRO_{base}.xlsx</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Allowed deviation for longitudinal impact % (CH_SC_17).</t>
+          <t>Macro workbook name; {base} = scenario base name (CH_NM_03).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>decel_tolerance_ms2</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.1</v>
+          <t>review_file_pattern</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>{base}_Review.xlsx</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Allowed deviation from the -4 m/s² braking value.</t>
+          <t>Manual review checklist name; {base} = scenario base name (optional, being phased out).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>speed_sanity_max_kmh</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>300</v>
+          <t>required_associated_roles</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>functional, macro</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Speeds above this are flagged as garbage data (CH_MR_01).</t>
+          <t>Which affix files are mandatory: functional, macro (review is optional).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>east_heading_tolerance_deg</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>30</v>
+          <t>junction_scenario_prefixes</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CP, CB, CCCscp, CMCscp, CCFtap, CMFtap</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Heading tolerance used by the lane-side check (CH_SC_05).</t>
+          <t>Scenario families that require junction geometry checks (RD_03-06, SC_10).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cardinal_heading_tolerance_deg</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>5</v>
+          <t>extra_scenario_prefixes</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CPRA</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How close to 0/90/180/270° the VUT heading must be (CH_SC_06).</t>
+          <t>Extra valid scenario name prefixes that have no row in the Scenarios sheet.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>right_lane_offset_threshold_m</t>
+          <t>junction_waypoint_radius_m</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1</v>
+        <v>20</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lateral offset that decides left vs right lane (CH_SC_05).</t>
+          <t>How close to a junction a waypoint must be to count as 'at the junction'.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>curvature_min_heading_delta_rad</t>
+          <t>lane_width_tolerance_m</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Minimum per-vertex heading change to count as turning (CH_SC_07).</t>
+          <t>Allowed deviation from the 3.5 m lane width.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>curvature_min_segment_length_m</t>
+          <t>junction_radius_tolerance_m</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minimum segment length used in turn-radius estimation (CH_SC_07).</t>
+          <t>Allowed deviation from the 8 m junction radius.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>impact_tolerance_pct</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Allowed deviation for crossing/turning impact % (CH_SC_16).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>longitudinal_impact_tolerance_pct</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Allowed deviation for longitudinal impact % (CH_SC_17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>decel_tolerance_ms2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Allowed deviation from the -4 m/s² braking value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>speed_sanity_max_kmh</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>300</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Speeds above this are flagged as garbage data (CH_MR_01).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>east_heading_tolerance_deg</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>30</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Heading tolerance used by the lane-side check (CH_SC_05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cardinal_heading_tolerance_deg</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>How close to 0/90/180/270° the VUT heading must be (CH_SC_06).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>right_lane_offset_threshold_m</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Lateral offset that decides left vs right lane (CH_SC_05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>curvature_min_heading_delta_rad</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Minimum per-vertex heading change to count as turning (CH_SC_07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>curvature_min_segment_length_m</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Minimum segment length used in turn-radius estimation (CH_SC_07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>curve_radius_tolerance_pct</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B34" t="n">
         <v>20</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Allowed deviation from the protocol Part 2 turn radius (CH_SC_07).</t>
         </is>
@@ -988,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1231,6 +1379,12 @@
           <t>crossing</t>
         </is>
       </c>
+      <c r="C8" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" t="n">
+        <v>80</v>
+      </c>
       <c r="F8" t="n">
         <v>50</v>
       </c>
@@ -1246,26 +1400,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CPNA-25</t>
+          <t>CPLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>crossing</t>
+          <t>longitudinal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
-      </c>
-      <c r="F9" t="n">
-        <v>25</v>
+        <v>80</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>crossing</t>
+          <t>left-to-right</t>
         </is>
       </c>
       <c r="H9" t="b">
@@ -1275,7 +1429,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CPNA-50</t>
+          <t>CPFA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1289,8 +1443,8 @@
       <c r="D10" t="n">
         <v>60</v>
       </c>
-      <c r="F10" t="n">
-        <v>50</v>
+      <c r="E10" t="n">
+        <v>5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1304,7 +1458,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CPNA-75</t>
+          <t>CPNA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1318,8 +1472,8 @@
       <c r="D11" t="n">
         <v>60</v>
       </c>
-      <c r="F11" t="n">
-        <v>75</v>
+      <c r="E11" t="n">
+        <v>5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1333,7 +1487,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CPFA-50</t>
+          <t>CPNCO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1347,6 +1501,9 @@
       <c r="D12" t="n">
         <v>60</v>
       </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
       <c r="F12" t="n">
         <v>50</v>
       </c>
@@ -1362,7 +1519,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CBNA-50</t>
+          <t>CPTA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1371,13 +1528,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>60</v>
       </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1391,20 +1551,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CBLA-25</t>
+          <t>CBFA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>longitudinal</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>25</v>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>60</v>
+      </c>
+      <c r="E14" t="n">
+        <v>20</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>left-to-right</t>
+          <t>crossing</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -1414,20 +1580,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CBLA-50</t>
+          <t>CBNA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>longitudinal</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>50</v>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" t="n">
+        <v>60</v>
+      </c>
+      <c r="E15" t="n">
+        <v>15</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>left-to-right</t>
+          <t>crossing</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -1437,7 +1609,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CPNCO</t>
+          <t>CBNAO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1446,16 +1618,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1469,38 +1638,168 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CPTA</t>
+          <t>CBLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>crossing</t>
+          <t>longitudinal</t>
         </is>
       </c>
       <c r="C17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" t="n">
+        <v>80</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>left-to-right</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CBTA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>10</v>
       </c>
-      <c r="D17" t="n">
-        <v>60</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" t="n">
+      <c r="D18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" t="n">
+        <v>15</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CMCscp</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" t="n">
+        <v>80</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CMFtap</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>10</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>crossing</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
+      <c r="D20" t="n">
+        <v>25</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CMRs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>longitudinal</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="n">
+        <v>80</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>left-to-right</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CMRb</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>longitudinal</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>30</v>
+      </c>
+      <c r="D22" t="n">
+        <v>130</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>left-to-right</t>
+        </is>
+      </c>
+      <c r="H22" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2 B3 B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B2 B3 B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"longitudinal,crossing,head-on"</formula1>
     </dataValidation>
   </dataValidations>

--- a/config.xlsx
+++ b/config.xlsx
@@ -894,17 +894,15 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>junction_scenario_prefixes</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CP, CB, CCCscp, CMCscp, CCFtap, CMFtap</t>
-        </is>
+          <t>junction_intersection_min_spread_deg</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>30</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scenario families that require junction geometry checks (RD_03-06, SC_10).</t>
+          <t>A junction counts as an intersection (RD_03-06, SC_10) when its incoming roads differ in heading by more than this (deg). Auto-detected from the .xodr - no scenario list.</t>
         </is>
       </c>
     </row>
@@ -1136,17 +1134,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1172,20 +1168,10 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>target_speed_kmh</t>
+          <t>side_impact</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>impact_overlap_pct</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>direction</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>has_sov</t>
         </is>
@@ -1208,18 +1194,10 @@
       <c r="D2" t="n">
         <v>80</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>left-to-right</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1240,15 +1218,10 @@
       <c r="D3" t="n">
         <v>79</v>
       </c>
-      <c r="F3" t="n">
-        <v>50</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>left-to-right</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1269,22 +1242,17 @@
       <c r="D4" t="n">
         <v>62</v>
       </c>
-      <c r="F4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>left-to-right</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CCFtap</t>
+          <t>CCCscp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1293,20 +1261,15 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
-      </c>
-      <c r="F5" t="n">
-        <v>50</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>crossing</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
+        <v>80</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1318,7 +1281,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>longitudinal</t>
+          <t>head-on</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1327,15 +1290,10 @@
       <c r="D6" t="n">
         <v>100</v>
       </c>
-      <c r="F6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>head-on</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1356,22 +1314,17 @@
       <c r="D7" t="n">
         <v>100</v>
       </c>
-      <c r="F7" t="n">
-        <v>50</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>crossing</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CCCscp</t>
+          <t>CCFtap</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1380,20 +1333,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
-      </c>
-      <c r="F8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>crossing</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
+        <v>25</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1414,15 +1362,10 @@
       <c r="D9" t="n">
         <v>80</v>
       </c>
-      <c r="E9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>left-to-right</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1443,15 +1386,10 @@
       <c r="D10" t="n">
         <v>60</v>
       </c>
-      <c r="E10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>crossing</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1472,15 +1410,10 @@
       <c r="D11" t="n">
         <v>60</v>
       </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>crossing</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1501,18 +1434,10 @@
       <c r="D12" t="n">
         <v>60</v>
       </c>
-      <c r="E12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" t="n">
-        <v>50</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>crossing</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1533,25 +1458,17 @@
       <c r="D13" t="n">
         <v>60</v>
       </c>
-      <c r="E13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>crossing</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CBFA</t>
+          <t>CPTAfo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1565,22 +1482,17 @@
       <c r="D14" t="n">
         <v>60</v>
       </c>
-      <c r="E14" t="n">
-        <v>20</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>crossing</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CBNA</t>
+          <t>CPTAfs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1594,22 +1506,17 @@
       <c r="D15" t="n">
         <v>60</v>
       </c>
-      <c r="E15" t="n">
-        <v>15</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>crossing</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CBNAO</t>
+          <t>CPTAno</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1623,48 +1530,41 @@
       <c r="D16" t="n">
         <v>60</v>
       </c>
-      <c r="E16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>crossing</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CBLA</t>
+          <t>CPTAns</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>longitudinal</t>
+          <t>crossing</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>left-to-right</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
+        <v>60</v>
+      </c>
+      <c r="E17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CBTA</t>
+          <t>CBFA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1676,24 +1576,19 @@
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
-      </c>
-      <c r="E18" t="n">
-        <v>15</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>crossing</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
+        <v>60</v>
+      </c>
+      <c r="E18" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CMCscp</t>
+          <t>CBNA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1702,24 +1597,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>80</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>crossing</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
+        <v>60</v>
+      </c>
+      <c r="E19" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CMFtap</t>
+          <t>CBNAO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1731,21 +1624,19 @@
         <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>crossing</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
+        <v>60</v>
+      </c>
+      <c r="E20" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CMRs</t>
+          <t>CBLA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1754,52 +1645,237 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D21" t="n">
         <v>80</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>left-to-right</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
+      <c r="E21" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>CBTA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CBTAfo</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CBTAfs</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="n">
+        <v>25</v>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CBTAno</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>25</v>
+      </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CBTAns</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10</v>
+      </c>
+      <c r="D26" t="n">
+        <v>25</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CMCscp</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>20</v>
+      </c>
+      <c r="D27" t="n">
+        <v>80</v>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CMFtap</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>25</v>
+      </c>
+      <c r="E28" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CMRs</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>longitudinal</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" t="n">
+        <v>80</v>
+      </c>
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>CMRb</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>longitudinal</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C30" t="n">
         <v>30</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D30" t="n">
         <v>130</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>left-to-right</t>
-        </is>
-      </c>
-      <c r="H22" t="b">
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2 B3 B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B2 B3 B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B27 B28 B29 B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"longitudinal,crossing,head-on"</formula1>
     </dataValidation>
   </dataValidations>

--- a/config.xlsx
+++ b/config.xlsx
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>60</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>60</v>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>60</v>
@@ -1840,7 +1840,7 @@
         <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -1864,7 +1864,7 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>

--- a/config.xlsx
+++ b/config.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LHT = drive on left (Japan/India/UK — EuroNCAP default). RHT inverts Farside/Nearside.</t>
+          <t>LHT = drive on left (Japan/India/UK - EuroNCAP default). RHT inverts Farside/Nearside.</t>
         </is>
       </c>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1115,6 +1115,51 @@
       <c r="C34" t="inlineStr">
         <is>
           <t>Allowed deviation from the protocol Part 2 turn radius (CH_SC_07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>junction_lane_width_min_m</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Minimum junction side/connecting-lane width (m); RD_01 grades connecting lanes against [this, lane_width_m].</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>impact_rotation_sensitivity_pct</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>25</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CH_SC_16/17: impact-% swing across the sync window above which the rotation-robust overlap-centre metric is used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>speed_range_tolerance_kmh</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CH_SC_18: km/h tolerance on the protocol speed range when speed is measured (no filename token).</t>
         </is>
       </c>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>impact_tolerance_class</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">

--- a/config.xlsx
+++ b/config.xlsx
@@ -1501,7 +1501,7 @@
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -1525,7 +1525,7 @@
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -1573,7 +1573,7 @@
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -1885,7 +1885,7 @@
         <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>

--- a/config.xlsx
+++ b/config.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Impact-overlap %s the filename token may take (CH_NM_02); exact value is checked by SC_16/17.</t>
+          <t>Fallback impact-overlap %s for a family whose Scenarios-sheet impact_overlaps is blank (CH_NM_04); exact value is checked by SC_16/17.</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1188,6 +1188,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1221,6 +1222,11 @@
           <t>has_sov</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>impact_overlaps</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1245,6 +1251,11 @@
       <c r="F2" t="b">
         <v>0</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-25, 0, 25, 50, 75, 100, 125</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1269,6 +1280,11 @@
       <c r="F3" t="b">
         <v>0</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-25, 0, 25, 50, 75, 100, 125</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1293,6 +1309,11 @@
       <c r="F4" t="b">
         <v>0</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-25, 0, 25, 50, 75, 100, 125</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1341,6 +1362,11 @@
       <c r="F6" t="b">
         <v>0</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>25, 50, 75, 100</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1365,6 +1391,11 @@
       <c r="F7" t="b">
         <v>1</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>25, 50, 75, 100</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1389,6 +1420,11 @@
       <c r="F8" t="b">
         <v>0</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1413,6 +1449,11 @@
       <c r="F9" t="b">
         <v>0</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1437,6 +1478,11 @@
       <c r="F10" t="b">
         <v>0</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75, 90</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1461,6 +1507,11 @@
       <c r="F11" t="b">
         <v>0</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75, 90</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1485,6 +1536,11 @@
       <c r="F12" t="b">
         <v>0</v>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>25, 50, 75</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1509,6 +1565,11 @@
       <c r="F13" t="b">
         <v>0</v>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75, 90</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1533,6 +1594,11 @@
       <c r="F14" t="b">
         <v>0</v>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75, 90</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1557,6 +1623,11 @@
       <c r="F15" t="b">
         <v>0</v>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75, 90</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1581,6 +1652,11 @@
       <c r="F16" t="b">
         <v>0</v>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75, 90</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1605,6 +1681,11 @@
       <c r="F17" t="b">
         <v>0</v>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75, 90</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1629,6 +1710,11 @@
       <c r="F18" t="b">
         <v>0</v>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75, 90</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1653,6 +1739,11 @@
       <c r="F19" t="b">
         <v>0</v>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75, 90</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1677,6 +1768,11 @@
       <c r="F20" t="b">
         <v>0</v>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75, 90</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1701,6 +1797,11 @@
       <c r="F21" t="b">
         <v>0</v>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1725,6 +1826,11 @@
       <c r="F22" t="b">
         <v>0</v>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75, 90</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1749,6 +1855,11 @@
       <c r="F23" t="b">
         <v>0</v>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75, 90</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1773,6 +1884,11 @@
       <c r="F24" t="b">
         <v>0</v>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0, 75, 100</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1797,6 +1913,11 @@
       <c r="F25" t="b">
         <v>0</v>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75, 90</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1821,6 +1942,11 @@
       <c r="F26" t="b">
         <v>0</v>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0, 75, 100</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1869,6 +1995,11 @@
       <c r="F28" t="b">
         <v>0</v>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1893,6 +2024,11 @@
       <c r="F29" t="b">
         <v>0</v>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75, 90</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1916,6 +2052,11 @@
       </c>
       <c r="F30" t="b">
         <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>10, 25, 50, 75, 90</t>
+        </is>
       </c>
     </row>
   </sheetData>
